--- a/check-lists/catalog-search.xlsx
+++ b/check-lists/catalog-search.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victo\Desktop\qa-automationexercise-testing\check-lists\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F94F5FF9-CE13-49C9-AE81-A9BB7560996D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2AC884C-6725-47C7-9AE1-812464A2822C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{9B4B0753-DA42-431D-8D5F-8F7C84571E74}"/>
   </bookViews>
